--- a/metadata/mass_spectrometry_imaging_V4.xlsx
+++ b/metadata/mass_spectrometry_imaging_V4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Häußermann\Documents\HSMannheim\10-Projekte\FDM\Dataverse-Kubernetes-Angepasst\metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\server\01_Projekte\171_BMBF_FDM\01_Verwaltung\03_Dokumentation\Meilensteine\M3.4 Test-Deployments erfolgreich\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475355CA-595E-4A87-80FD-0A1B9BBE6944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676B782C-4791-43B7-AC8B-EA8C41254686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mass_spectrometry_imaging" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="238">
   <si>
     <t>#metadataBlock</t>
   </si>
@@ -174,12 +174,6 @@
   </si>
   <si>
     <t>Laser repetition rate (kHz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processing </t>
-  </si>
-  <si>
-    <t>List of the pre-processing steps / pipeline used on the raw data.</t>
   </si>
   <si>
     <t xml:space="preserve">Normalization </t>
@@ -484,9 +478,6 @@
     <t>laserRepRate_msi</t>
   </si>
   <si>
-    <t>processing_msi</t>
-  </si>
-  <si>
     <t>normalization_msi</t>
   </si>
   <si>
@@ -632,15 +623,6 @@
   </si>
   <si>
     <t>Description of other laser spot size used.</t>
-  </si>
-  <si>
-    <t>other_processing_msi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other processing </t>
-  </si>
-  <si>
-    <t>Description of other processing used.</t>
   </si>
   <si>
     <t>other_analyte_msi</t>
@@ -1718,19 +1700,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q152"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q146"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" customWidth="1"/>
-    <col min="5" max="5" width="14.1796875" customWidth="1"/>
-    <col min="10" max="10" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1747,18 +1729,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1811,129 +1793,129 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -1942,80 +1924,80 @@
         <v>3</v>
       </c>
       <c r="I7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" t="s">
         <v>170</v>
-      </c>
-      <c r="C8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F8" t="s">
-        <v>173</v>
       </c>
       <c r="G8">
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
@@ -2030,80 +2012,80 @@
         <v>5</v>
       </c>
       <c r="I9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q9" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G10">
         <v>6</v>
       </c>
       <c r="I10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
@@ -2118,36 +2100,36 @@
         <v>7</v>
       </c>
       <c r="I11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -2162,86 +2144,86 @@
         <v>8</v>
       </c>
       <c r="I12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G13">
         <v>9</v>
       </c>
       <c r="I13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q13" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -2250,86 +2232,86 @@
         <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O14" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q14" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G15">
         <v>11</v>
       </c>
       <c r="I15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O15" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q15" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C16" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -2338,80 +2320,80 @@
         <v>12</v>
       </c>
       <c r="I16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O16" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q16" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C17" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G17">
         <v>13</v>
       </c>
       <c r="I17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O17" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q17" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
         <v>29</v>
@@ -2426,83 +2408,83 @@
         <v>14</v>
       </c>
       <c r="I18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O18" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q18" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D19" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G19">
         <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J19" t="s">
+        <v>107</v>
+      </c>
+      <c r="K19" t="s">
+        <v>107</v>
+      </c>
+      <c r="L19" t="s">
+        <v>107</v>
+      </c>
+      <c r="M19" t="s">
+        <v>108</v>
+      </c>
+      <c r="N19" t="s">
+        <v>107</v>
+      </c>
+      <c r="O19" t="s">
+        <v>153</v>
+      </c>
+      <c r="P19" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" t="s">
         <v>109</v>
-      </c>
-      <c r="K19" t="s">
-        <v>109</v>
-      </c>
-      <c r="L19" t="s">
-        <v>109</v>
-      </c>
-      <c r="M19" t="s">
-        <v>110</v>
-      </c>
-      <c r="N19" t="s">
-        <v>109</v>
-      </c>
-      <c r="O19" t="s">
-        <v>156</v>
-      </c>
-      <c r="P19" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
@@ -2514,39 +2496,39 @@
         <v>16</v>
       </c>
       <c r="I20" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" t="s">
+        <v>107</v>
+      </c>
+      <c r="K20" t="s">
+        <v>107</v>
+      </c>
+      <c r="L20" t="s">
+        <v>107</v>
+      </c>
+      <c r="M20" t="s">
+        <v>108</v>
+      </c>
+      <c r="N20" t="s">
+        <v>107</v>
+      </c>
+      <c r="O20" t="s">
+        <v>153</v>
+      </c>
+      <c r="P20" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
         <v>110</v>
-      </c>
-      <c r="J20" t="s">
-        <v>109</v>
-      </c>
-      <c r="K20" t="s">
-        <v>109</v>
-      </c>
-      <c r="L20" t="s">
-        <v>109</v>
-      </c>
-      <c r="M20" t="s">
-        <v>110</v>
-      </c>
-      <c r="N20" t="s">
-        <v>109</v>
-      </c>
-      <c r="O20" t="s">
-        <v>156</v>
-      </c>
-      <c r="P20" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -2558,36 +2540,36 @@
         <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O21" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q21" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -2602,80 +2584,80 @@
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O22" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q22" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C23" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D23" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F23" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G23">
         <v>19</v>
       </c>
       <c r="I23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q23" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C24" t="s">
         <v>35</v>
@@ -2690,42 +2672,42 @@
         <v>20</v>
       </c>
       <c r="I24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O24" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q24" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D25" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2734,86 +2716,86 @@
         <v>21</v>
       </c>
       <c r="I25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O25" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q25" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C26" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D26" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F26" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G26">
         <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O26" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q26" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
         <v>43</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2822,36 +2804,36 @@
         <v>23</v>
       </c>
       <c r="I27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N27" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O27" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q27" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
         <v>44</v>
@@ -2866,42 +2848,42 @@
         <v>24</v>
       </c>
       <c r="I28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O28" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q28" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D29" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2910,36 +2892,36 @@
         <v>25</v>
       </c>
       <c r="I29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N29" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O29" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q29" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s">
         <v>46</v>
@@ -2954,86 +2936,86 @@
         <v>26</v>
       </c>
       <c r="I30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O30" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q30" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="D31" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="F31" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="G31">
         <v>27</v>
       </c>
       <c r="I31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O31" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P31" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q31" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -3042,42 +3024,42 @@
         <v>28</v>
       </c>
       <c r="I32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O32" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P32" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q32" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D33" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -3086,86 +3068,86 @@
         <v>29</v>
       </c>
       <c r="I33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O33" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q33" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>213</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="G34">
         <v>30</v>
       </c>
       <c r="I34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N34" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O34" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q34" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>216</v>
       </c>
       <c r="C35" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D35" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -3174,86 +3156,86 @@
         <v>31</v>
       </c>
       <c r="I35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O35" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q35" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" t="s">
-        <v>218</v>
-      </c>
-      <c r="D36" t="s">
-        <v>219</v>
-      </c>
-      <c r="F36" t="s">
-        <v>173</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="G36">
         <v>32</v>
       </c>
-      <c r="I36" t="s">
-        <v>110</v>
-      </c>
-      <c r="J36" t="s">
-        <v>109</v>
-      </c>
-      <c r="K36" t="s">
-        <v>109</v>
-      </c>
-      <c r="L36" t="s">
-        <v>109</v>
-      </c>
-      <c r="M36" t="s">
-        <v>110</v>
-      </c>
-      <c r="N36" t="s">
-        <v>109</v>
-      </c>
-      <c r="O36" t="s">
-        <v>157</v>
-      </c>
-      <c r="P36" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="I36" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q36" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C37" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D37" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -3262,86 +3244,86 @@
         <v>33</v>
       </c>
       <c r="I37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q37" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="38" spans="2:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>173</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" t="s">
+        <v>225</v>
+      </c>
+      <c r="F38" t="s">
+        <v>170</v>
       </c>
       <c r="G38">
         <v>34</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="L38" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="N38" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="O38" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="P38" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q38" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="I38" t="s">
+        <v>108</v>
+      </c>
+      <c r="J38" t="s">
+        <v>107</v>
+      </c>
+      <c r="K38" t="s">
+        <v>107</v>
+      </c>
+      <c r="L38" t="s">
+        <v>107</v>
+      </c>
+      <c r="M38" t="s">
+        <v>108</v>
+      </c>
+      <c r="N38" t="s">
+        <v>107</v>
+      </c>
+      <c r="O38" t="s">
+        <v>154</v>
+      </c>
+      <c r="P38" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C39" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D39" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F39" t="s">
         <v>21</v>
@@ -3350,86 +3332,86 @@
         <v>35</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O39" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P39" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q39" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C40" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D40" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F40" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G40">
         <v>36</v>
       </c>
       <c r="I40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q40" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>226</v>
+        <v>130</v>
       </c>
       <c r="C41" t="s">
-        <v>227</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>213</v>
+        <v>40</v>
       </c>
       <c r="F41" t="s">
         <v>21</v>
@@ -3438,86 +3420,86 @@
         <v>37</v>
       </c>
       <c r="I41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O41" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q41" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="C42" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="D42" t="s">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="F42" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G42">
         <v>38</v>
       </c>
       <c r="I42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O42" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P42" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q42" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D43" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F43" t="s">
         <v>21</v>
@@ -3526,218 +3508,218 @@
         <v>39</v>
       </c>
       <c r="I43" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J43" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K43" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M43" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N43" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O43" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P43" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q43" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C44" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D44" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F44" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G44">
         <v>40</v>
       </c>
       <c r="I44" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M44" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N44" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O44" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P44" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q44" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B45" t="s">
-        <v>133</v>
-      </c>
-      <c r="C45" t="s">
-        <v>41</v>
-      </c>
-      <c r="D45" t="s">
-        <v>42</v>
-      </c>
-      <c r="F45" t="s">
-        <v>21</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="G45">
         <v>41</v>
       </c>
-      <c r="I45" t="s">
-        <v>110</v>
-      </c>
-      <c r="J45" t="s">
-        <v>110</v>
-      </c>
-      <c r="K45" t="s">
-        <v>109</v>
-      </c>
-      <c r="L45" t="s">
-        <v>109</v>
-      </c>
-      <c r="M45" t="s">
-        <v>110</v>
-      </c>
-      <c r="N45" t="s">
-        <v>109</v>
-      </c>
-      <c r="O45" t="s">
-        <v>157</v>
-      </c>
-      <c r="P45" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q45" t="s">
+      <c r="I45" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="M45" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O45" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="P45" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q45" s="7" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="C46" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F46" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="G46">
         <v>42</v>
       </c>
       <c r="I46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N46" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O46" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P46" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q46" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17" s="7" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>173</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>199</v>
+      </c>
+      <c r="C47" t="s">
+        <v>195</v>
+      </c>
+      <c r="D47" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" t="s">
+        <v>170</v>
       </c>
       <c r="G47">
         <v>43</v>
       </c>
-      <c r="I47" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="L47" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="M47" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="N47" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="O47" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="P47" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q47" s="7" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="I47" t="s">
+        <v>108</v>
+      </c>
+      <c r="J47" t="s">
+        <v>107</v>
+      </c>
+      <c r="K47" t="s">
+        <v>107</v>
+      </c>
+      <c r="L47" t="s">
+        <v>107</v>
+      </c>
+      <c r="M47" t="s">
+        <v>108</v>
+      </c>
+      <c r="N47" t="s">
+        <v>107</v>
+      </c>
+      <c r="O47" t="s">
+        <v>155</v>
+      </c>
+      <c r="P47" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D48" t="s">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -3746,86 +3728,86 @@
         <v>44</v>
       </c>
       <c r="I48" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J48" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M48" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N48" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O48" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P48" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q48" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>205</v>
+        <v>136</v>
       </c>
       <c r="C49" t="s">
-        <v>201</v>
+        <v>48</v>
       </c>
       <c r="D49" t="s">
-        <v>202</v>
+        <v>50</v>
       </c>
       <c r="F49" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="G49">
         <v>45</v>
       </c>
       <c r="I49" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M49" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O49" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P49" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q49" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F50" t="s">
         <v>21</v>
@@ -3834,1257 +3816,1125 @@
         <v>46</v>
       </c>
       <c r="I50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J50" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O50" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q50" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>139</v>
+        <v>234</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F51" t="s">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="G51">
         <v>47</v>
       </c>
       <c r="I51" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M51" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O51" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P51" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53" t="s">
         <v>113</v>
       </c>
-      <c r="Q51" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B52" t="s">
-        <v>140</v>
-      </c>
-      <c r="C52" t="s">
-        <v>53</v>
-      </c>
-      <c r="D52" t="s">
-        <v>54</v>
-      </c>
-      <c r="F52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G52">
-        <v>48</v>
-      </c>
-      <c r="I52" t="s">
-        <v>110</v>
-      </c>
-      <c r="J52" t="s">
-        <v>109</v>
-      </c>
-      <c r="K52" t="s">
-        <v>109</v>
-      </c>
-      <c r="L52" t="s">
-        <v>109</v>
-      </c>
-      <c r="M52" t="s">
-        <v>110</v>
-      </c>
-      <c r="N52" t="s">
-        <v>109</v>
-      </c>
-      <c r="O52" t="s">
-        <v>158</v>
-      </c>
-      <c r="P52" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B53" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" t="s">
-        <v>149</v>
-      </c>
-      <c r="D53" t="s">
-        <v>55</v>
-      </c>
-      <c r="F53" t="s">
-        <v>173</v>
-      </c>
-      <c r="G53">
-        <v>49</v>
-      </c>
-      <c r="I53" t="s">
-        <v>110</v>
-      </c>
-      <c r="J53" t="s">
-        <v>109</v>
-      </c>
-      <c r="K53" t="s">
-        <v>109</v>
-      </c>
-      <c r="L53" t="s">
-        <v>109</v>
-      </c>
-      <c r="M53" t="s">
-        <v>110</v>
-      </c>
-      <c r="N53" t="s">
-        <v>109</v>
-      </c>
-      <c r="O53" t="s">
-        <v>158</v>
-      </c>
-      <c r="P53" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>56</v>
-      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="C54" t="s">
-        <v>58</v>
-      </c>
-      <c r="D54" t="s">
-        <v>59</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C55" t="s">
         <v>115</v>
       </c>
       <c r="E55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C56" t="s">
         <v>116</v>
       </c>
       <c r="E56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
         <v>117</v>
       </c>
       <c r="E57">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="E58">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C59" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="E59">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C60" t="s">
         <v>60</v>
       </c>
       <c r="E60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C61" t="s">
         <v>61</v>
       </c>
       <c r="E61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C62" t="s">
         <v>62</v>
       </c>
       <c r="E62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C63" t="s">
         <v>63</v>
       </c>
       <c r="E63">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C64" t="s">
         <v>64</v>
       </c>
       <c r="E64">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C65" t="s">
         <v>65</v>
       </c>
       <c r="E65">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C66" t="s">
         <v>66</v>
       </c>
       <c r="E66">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C67" t="s">
         <v>67</v>
       </c>
       <c r="E67">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C68" t="s">
-        <v>68</v>
+        <v>198</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C69" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C70" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="E70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>123</v>
+      </c>
+      <c r="C71" t="s">
+        <v>149</v>
+      </c>
+      <c r="E71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>123</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E72">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>123</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>123</v>
+      </c>
+      <c r="C75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E75">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" t="s">
+        <v>156</v>
+      </c>
+      <c r="E76">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B71" t="s">
-        <v>125</v>
-      </c>
-      <c r="C71" t="s">
-        <v>150</v>
-      </c>
-      <c r="E71">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>143</v>
+      </c>
+      <c r="C77" t="s">
+        <v>157</v>
+      </c>
+      <c r="E77">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B72" t="s">
-        <v>125</v>
-      </c>
-      <c r="C72" t="s">
-        <v>151</v>
-      </c>
-      <c r="E72">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" t="s">
+        <v>158</v>
+      </c>
+      <c r="E78">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B73" t="s">
-        <v>125</v>
-      </c>
-      <c r="C73" t="s">
-        <v>152</v>
-      </c>
-      <c r="E73">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>143</v>
+      </c>
+      <c r="C79" t="s">
+        <v>65</v>
+      </c>
+      <c r="E79">
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B74" t="s">
-        <v>125</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E74">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B75" t="s">
-        <v>125</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E75">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>205</v>
+      </c>
+      <c r="C80" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>205</v>
+      </c>
+      <c r="C81" t="s">
+        <v>78</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>159</v>
+      </c>
+      <c r="C82" s="6">
         <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B76" t="s">
-        <v>125</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E76">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B77" t="s">
-        <v>125</v>
-      </c>
-      <c r="C77" t="s">
-        <v>67</v>
-      </c>
-      <c r="E77">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B78" t="s">
-        <v>146</v>
-      </c>
-      <c r="C78" t="s">
-        <v>159</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B79" t="s">
-        <v>146</v>
-      </c>
-      <c r="C79" t="s">
-        <v>160</v>
-      </c>
-      <c r="E79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B80" t="s">
-        <v>146</v>
-      </c>
-      <c r="C80" t="s">
-        <v>161</v>
-      </c>
-      <c r="E80">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B81" t="s">
-        <v>146</v>
-      </c>
-      <c r="C81" t="s">
-        <v>67</v>
-      </c>
-      <c r="E81">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B82" t="s">
-        <v>211</v>
-      </c>
-      <c r="C82" t="s">
-        <v>79</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>211</v>
-      </c>
-      <c r="C83" t="s">
-        <v>80</v>
+        <v>159</v>
+      </c>
+      <c r="C83" s="6">
+        <v>10</v>
       </c>
       <c r="E83">
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C84" s="6">
+        <v>20</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="6">
+        <v>50</v>
+      </c>
+      <c r="E85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>159</v>
+      </c>
+      <c r="C86" s="6">
+        <v>100</v>
+      </c>
+      <c r="E86">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>159</v>
+      </c>
+      <c r="C87" s="6">
+        <v>200</v>
+      </c>
+      <c r="E87">
         <v>5</v>
       </c>
-      <c r="E84">
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>159</v>
+      </c>
+      <c r="C88" t="s">
+        <v>65</v>
+      </c>
+      <c r="E88">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>215</v>
+      </c>
+      <c r="C89" t="s">
+        <v>77</v>
+      </c>
+      <c r="E89">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B85" t="s">
-        <v>162</v>
-      </c>
-      <c r="C85" s="6">
-        <v>10</v>
-      </c>
-      <c r="E85">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>215</v>
+      </c>
+      <c r="C90" t="s">
+        <v>78</v>
+      </c>
+      <c r="E90">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B86" t="s">
-        <v>162</v>
-      </c>
-      <c r="C86" s="6">
-        <v>20</v>
-      </c>
-      <c r="E86">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B87" t="s">
-        <v>162</v>
-      </c>
-      <c r="C87" s="6">
-        <v>50</v>
-      </c>
-      <c r="E87">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B88" t="s">
-        <v>162</v>
-      </c>
-      <c r="C88" s="6">
-        <v>100</v>
-      </c>
-      <c r="E88">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B89" t="s">
-        <v>162</v>
-      </c>
-      <c r="C89" s="6">
-        <v>200</v>
-      </c>
-      <c r="E89">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B90" t="s">
-        <v>162</v>
-      </c>
-      <c r="C90" t="s">
-        <v>67</v>
-      </c>
-      <c r="E90">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="C91" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="C92" t="s">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="E92">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="C93" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="E93">
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="C94" t="s">
-        <v>67</v>
+        <v>230</v>
       </c>
       <c r="E94">
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C95" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E95">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>216</v>
+      </c>
+      <c r="C96" t="s">
+        <v>77</v>
+      </c>
+      <c r="E96">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B96" t="s">
-        <v>221</v>
-      </c>
-      <c r="C96" t="s">
-        <v>80</v>
-      </c>
-      <c r="E96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>216</v>
       </c>
       <c r="C97" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>218</v>
+      </c>
+      <c r="C98" t="s">
+        <v>77</v>
+      </c>
+      <c r="E98">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B98" t="s">
-        <v>216</v>
-      </c>
-      <c r="C98" t="s">
-        <v>80</v>
-      </c>
-      <c r="E98">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>218</v>
+      </c>
+      <c r="C99" t="s">
+        <v>78</v>
+      </c>
+      <c r="E99">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B99" t="s">
-        <v>216</v>
-      </c>
-      <c r="C99" t="s">
-        <v>235</v>
-      </c>
-      <c r="E99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C100" t="s">
-        <v>236</v>
+        <v>77</v>
       </c>
       <c r="E100">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C101" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E101">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>222</v>
+        <v>124</v>
       </c>
       <c r="C102" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E102">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>222</v>
+        <v>124</v>
       </c>
       <c r="C103" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>224</v>
+        <v>124</v>
       </c>
       <c r="C104" t="s">
+        <v>70</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>124</v>
+      </c>
+      <c r="C105" t="s">
+        <v>71</v>
+      </c>
+      <c r="E105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>124</v>
+      </c>
+      <c r="C106" t="s">
+        <v>65</v>
+      </c>
+      <c r="E106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>127</v>
+      </c>
+      <c r="C107" t="s">
+        <v>72</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>127</v>
+      </c>
+      <c r="C108" t="s">
+        <v>73</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>127</v>
+      </c>
+      <c r="C109" t="s">
+        <v>74</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>127</v>
+      </c>
+      <c r="C110" t="s">
+        <v>75</v>
+      </c>
+      <c r="E110">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>127</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E111">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>127</v>
+      </c>
+      <c r="C112" t="s">
+        <v>65</v>
+      </c>
+      <c r="E112">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>130</v>
+      </c>
+      <c r="C113" t="s">
         <v>79</v>
-      </c>
-      <c r="E104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B105" t="s">
-        <v>224</v>
-      </c>
-      <c r="C105" t="s">
-        <v>80</v>
-      </c>
-      <c r="E105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B106" t="s">
-        <v>226</v>
-      </c>
-      <c r="C106" t="s">
-        <v>79</v>
-      </c>
-      <c r="E106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B107" t="s">
-        <v>226</v>
-      </c>
-      <c r="C107" t="s">
-        <v>80</v>
-      </c>
-      <c r="E107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B108" t="s">
-        <v>126</v>
-      </c>
-      <c r="C108" t="s">
-        <v>70</v>
-      </c>
-      <c r="E108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B109" t="s">
-        <v>126</v>
-      </c>
-      <c r="C109" t="s">
-        <v>71</v>
-      </c>
-      <c r="E109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B110" t="s">
-        <v>126</v>
-      </c>
-      <c r="C110" t="s">
-        <v>72</v>
-      </c>
-      <c r="E110">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B111" t="s">
-        <v>126</v>
-      </c>
-      <c r="C111" t="s">
-        <v>73</v>
-      </c>
-      <c r="E111">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B112" t="s">
-        <v>126</v>
-      </c>
-      <c r="C112" t="s">
-        <v>67</v>
-      </c>
-      <c r="E112">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B113" t="s">
-        <v>129</v>
-      </c>
-      <c r="C113" t="s">
-        <v>74</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C114" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E114">
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C115" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E115">
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C116" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E116">
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>129</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>78</v>
+        <v>130</v>
+      </c>
+      <c r="C117" t="s">
+        <v>83</v>
       </c>
       <c r="E117">
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C118" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E118">
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C119" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E119">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C120" t="s">
+        <v>86</v>
+      </c>
+      <c r="E120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>130</v>
+      </c>
+      <c r="C121" t="s">
+        <v>87</v>
+      </c>
+      <c r="E121">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>130</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E122">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>130</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E123">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>130</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E124">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>130</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E125">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>130</v>
+      </c>
+      <c r="C126" t="s">
+        <v>65</v>
+      </c>
+      <c r="E126">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>131</v>
+      </c>
+      <c r="C127" t="s">
+        <v>92</v>
+      </c>
+      <c r="E127">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B120" t="s">
-        <v>132</v>
-      </c>
-      <c r="C120" t="s">
-        <v>82</v>
-      </c>
-      <c r="E120">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>131</v>
+      </c>
+      <c r="C128" t="s">
+        <v>93</v>
+      </c>
+      <c r="E128">
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B121" t="s">
-        <v>132</v>
-      </c>
-      <c r="C121" t="s">
-        <v>83</v>
-      </c>
-      <c r="E121">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>131</v>
+      </c>
+      <c r="C129" t="s">
+        <v>94</v>
+      </c>
+      <c r="E129">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B122" t="s">
-        <v>132</v>
-      </c>
-      <c r="C122" t="s">
-        <v>84</v>
-      </c>
-      <c r="E122">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>131</v>
+      </c>
+      <c r="C130" t="s">
+        <v>95</v>
+      </c>
+      <c r="E130">
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B123" t="s">
-        <v>132</v>
-      </c>
-      <c r="C123" t="s">
-        <v>85</v>
-      </c>
-      <c r="E123">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>131</v>
+      </c>
+      <c r="C131" t="s">
+        <v>96</v>
+      </c>
+      <c r="E131">
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B124" t="s">
-        <v>132</v>
-      </c>
-      <c r="C124" t="s">
-        <v>86</v>
-      </c>
-      <c r="E124">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>131</v>
+      </c>
+      <c r="C132" t="s">
+        <v>97</v>
+      </c>
+      <c r="E132">
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B125" t="s">
-        <v>132</v>
-      </c>
-      <c r="C125" t="s">
-        <v>87</v>
-      </c>
-      <c r="E125">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>131</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E133">
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B126" t="s">
-        <v>132</v>
-      </c>
-      <c r="C126" t="s">
-        <v>88</v>
-      </c>
-      <c r="E126">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>131</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E134">
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B127" t="s">
-        <v>132</v>
-      </c>
-      <c r="C127" t="s">
-        <v>89</v>
-      </c>
-      <c r="E127">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>131</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E135">
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B128" t="s">
-        <v>132</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E128">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>131</v>
+      </c>
+      <c r="C136" t="s">
+        <v>65</v>
+      </c>
+      <c r="E136">
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B129" t="s">
-        <v>132</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E129">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B130" t="s">
-        <v>132</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E130">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B131" t="s">
-        <v>132</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E131">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B132" t="s">
-        <v>132</v>
-      </c>
-      <c r="C132" t="s">
-        <v>67</v>
-      </c>
-      <c r="E132">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B133" t="s">
-        <v>133</v>
-      </c>
-      <c r="C133" t="s">
-        <v>94</v>
-      </c>
-      <c r="E133">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>138</v>
+      </c>
+      <c r="C137" t="s">
+        <v>101</v>
+      </c>
+      <c r="E137">
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B134" t="s">
-        <v>133</v>
-      </c>
-      <c r="C134" t="s">
-        <v>95</v>
-      </c>
-      <c r="E134">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>138</v>
+      </c>
+      <c r="C138" t="s">
+        <v>102</v>
+      </c>
+      <c r="E138">
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B135" t="s">
-        <v>133</v>
-      </c>
-      <c r="C135" t="s">
-        <v>96</v>
-      </c>
-      <c r="E135">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>138</v>
+      </c>
+      <c r="C139" t="s">
+        <v>118</v>
+      </c>
+      <c r="E139">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B136" t="s">
-        <v>133</v>
-      </c>
-      <c r="C136" t="s">
-        <v>97</v>
-      </c>
-      <c r="E136">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>138</v>
+      </c>
+      <c r="C140" t="s">
+        <v>103</v>
+      </c>
+      <c r="E140">
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B137" t="s">
-        <v>133</v>
-      </c>
-      <c r="C137" t="s">
-        <v>98</v>
-      </c>
-      <c r="E137">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>138</v>
+      </c>
+      <c r="C141" t="s">
+        <v>104</v>
+      </c>
+      <c r="E141">
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B138" t="s">
-        <v>133</v>
-      </c>
-      <c r="C138" t="s">
-        <v>99</v>
-      </c>
-      <c r="E138">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>138</v>
+      </c>
+      <c r="C142" t="s">
+        <v>105</v>
+      </c>
+      <c r="E142">
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B139" t="s">
-        <v>133</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E139">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>138</v>
+      </c>
+      <c r="C143" t="s">
+        <v>106</v>
+      </c>
+      <c r="E143">
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B140" t="s">
-        <v>133</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E140">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>138</v>
+      </c>
+      <c r="C144" t="s">
+        <v>65</v>
+      </c>
+      <c r="E144">
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B141" t="s">
-        <v>133</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E141">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B142" t="s">
-        <v>133</v>
-      </c>
-      <c r="C142" t="s">
-        <v>67</v>
-      </c>
-      <c r="E142">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B143" t="s">
-        <v>141</v>
-      </c>
-      <c r="C143" t="s">
-        <v>103</v>
-      </c>
-      <c r="E143">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>135</v>
+      </c>
+      <c r="C145" t="s">
+        <v>77</v>
+      </c>
+      <c r="E145">
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B144" t="s">
-        <v>141</v>
-      </c>
-      <c r="C144" t="s">
-        <v>104</v>
-      </c>
-      <c r="E144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B145" t="s">
-        <v>141</v>
-      </c>
-      <c r="C145" t="s">
-        <v>120</v>
-      </c>
-      <c r="E145">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C146" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E146">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B147" t="s">
-        <v>141</v>
-      </c>
-      <c r="C147" t="s">
-        <v>106</v>
-      </c>
-      <c r="E147">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B148" t="s">
-        <v>141</v>
-      </c>
-      <c r="C148" t="s">
-        <v>107</v>
-      </c>
-      <c r="E148">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B149" t="s">
-        <v>141</v>
-      </c>
-      <c r="C149" t="s">
-        <v>108</v>
-      </c>
-      <c r="E149">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B150" t="s">
-        <v>141</v>
-      </c>
-      <c r="C150" t="s">
-        <v>67</v>
-      </c>
-      <c r="E150">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B151" t="s">
-        <v>138</v>
-      </c>
-      <c r="C151" t="s">
-        <v>79</v>
-      </c>
-      <c r="E151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B152" t="s">
-        <v>138</v>
-      </c>
-      <c r="C152" t="s">
-        <v>80</v>
-      </c>
-      <c r="E152">
         <v>1</v>
       </c>
     </row>
